--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/IOWA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/IOWA_2013.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C81">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C100">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C398">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C592">
